--- a/data/trans_orig/P16A07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A07-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31527</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>39962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259957</t>
+          <t>259879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270272</t>
+          <t>270248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229311</t>
+          <t>228446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247288</t>
+          <t>247524</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>494836</t>
+          <t>493886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>515142</t>
+          <t>515196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40519</t>
+          <t>41042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>23017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48382</t>
+          <t>45555</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484046</t>
+          <t>484186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492080</t>
+          <t>492092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463430</t>
+          <t>462907</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484221</t>
+          <t>484217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>948642</t>
+          <t>951469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>972894</t>
+          <t>974007</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24538</t>
+          <t>23799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30098</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308096</t>
+          <t>306520</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317827</t>
+          <t>317822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310874</t>
+          <t>311613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326475</t>
+          <t>326575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624160</t>
+          <t>624992</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>642342</t>
+          <t>643062</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>26131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>12513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28958</t>
+          <t>29254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>350905</t>
+          <t>350190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357822</t>
+          <t>357815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346049</t>
+          <t>345325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361410</t>
+          <t>361178</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>701169</t>
+          <t>700873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717692</t>
+          <t>717614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,82 +2120,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>23693</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15522</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35517</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>11,41%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>32695</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>23008</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>44330</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>23693</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>15422</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>34433</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>32695</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>23444</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>44257</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187130</t>
+          <t>188296</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198761</t>
+          <t>198876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,82 +2233,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>92,62%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>183975</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>172151</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>192146</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>88,59%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>82,9%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>92,53%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>378281</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>366646</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>387968</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>92,04%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>183975</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>173235</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>192246</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>88,59%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>83,42%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>92,57%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>378281</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>366719</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>387532</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264161</t>
+          <t>263627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261931</t>
+          <t>261705</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274062</t>
+          <t>273343</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>530710</t>
+          <t>529184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542960</t>
+          <t>542963</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>19497</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35780</t>
+          <t>36091</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64119</t>
+          <t>61675</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46760</t>
+          <t>46409</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76124</t>
+          <t>75460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595262</t>
+          <t>595530</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>608631</t>
+          <t>608790</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>574100</t>
+          <t>576544</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>602439</t>
+          <t>602128</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1177122</t>
+          <t>1177786</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1206486</t>
+          <t>1206837</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20346</t>
+          <t>19612</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43534</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42018</t>
+          <t>42147</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71955</t>
+          <t>71657</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67403</t>
+          <t>66197</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105862</t>
+          <t>105297</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699243</t>
+          <t>700956</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>722431</t>
+          <t>723165</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>711556</t>
+          <t>711854</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>741493</t>
+          <t>741364</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1420426</t>
+          <t>1420991</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1458885</t>
+          <t>1460091</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>55089</t>
+          <t>55132</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85755</t>
+          <t>88484</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190280</t>
+          <t>190996</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>246748</t>
+          <t>247695</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>255230</t>
+          <t>259067</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>320257</t>
+          <t>319516</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3189770</t>
+          <t>3187041</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3220436</t>
+          <t>3220393</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3132449</t>
+          <t>3131502</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3188917</t>
+          <t>3188201</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6334465</t>
+          <t>6335206</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6399492</t>
+          <t>6395655</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33219</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22328</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>44136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>270704</t>
+          <t>270694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284470</t>
+          <t>284303</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248846</t>
+          <t>250508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268666</t>
+          <t>268290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>527309</t>
+          <t>528133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>549941</t>
+          <t>550290</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>24630</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>31313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56506</t>
+          <t>56830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>42145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73259</t>
+          <t>73071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>478144</t>
+          <t>479856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>498339</t>
+          <t>499087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466225</t>
+          <t>465901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491715</t>
+          <t>491418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953958</t>
+          <t>954146</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>986998</t>
+          <t>985072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6899</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22311</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21389</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42694</t>
+          <t>42193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32741</t>
+          <t>31901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60046</t>
+          <t>57701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300805</t>
+          <t>300214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316217</t>
+          <t>316112</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>298326</t>
+          <t>298827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319631</t>
+          <t>320981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>604090</t>
+          <t>606435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>631395</t>
+          <t>632235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29517</t>
+          <t>29348</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>52799</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32958</t>
+          <t>33220</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58340</t>
+          <t>59979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>362447</t>
+          <t>363135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371946</t>
+          <t>371940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>335918</t>
+          <t>335175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358457</t>
+          <t>358626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>703616</t>
+          <t>701977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728998</t>
+          <t>728736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12758</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45474</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>28030</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54114</t>
+          <t>54145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199860</t>
+          <t>198702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210443</t>
+          <t>210439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174117</t>
+          <t>173978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>196069</t>
+          <t>195206</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378095</t>
+          <t>378064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>403193</t>
+          <t>404179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>17760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15787</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33883</t>
+          <t>35327</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24187</t>
+          <t>25334</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46655</t>
+          <t>48230</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255038</t>
+          <t>256221</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268826</t>
+          <t>268963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245257</t>
+          <t>243813</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263353</t>
+          <t>262794</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>506466</t>
+          <t>504891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>528934</t>
+          <t>527787</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41124</t>
+          <t>42083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38105</t>
+          <t>37476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66177</t>
+          <t>65578</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63215</t>
+          <t>63140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98802</t>
+          <t>100962</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>621664</t>
+          <t>620705</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>644193</t>
+          <t>643991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>626596</t>
+          <t>627195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>654668</t>
+          <t>655297</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1256759</t>
+          <t>1254599</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1292346</t>
+          <t>1292421</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32960</t>
+          <t>33180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41374</t>
+          <t>41003</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68764</t>
+          <t>72133</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59379</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95867</t>
+          <t>92989</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>744012</t>
+          <t>743792</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764189</t>
+          <t>765281</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>752756</t>
+          <t>749387</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>780146</t>
+          <t>780517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1502625</t>
+          <t>1505503</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1539113</t>
+          <t>1541151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>86572</t>
+          <t>86537</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>133555</t>
+          <t>132995</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>262752</t>
+          <t>264554</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>328478</t>
+          <t>331394</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>367529</t>
+          <t>364473</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>448340</t>
+          <t>448511</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3284592</t>
+          <t>3285152</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3331575</t>
+          <t>3331610</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3218337</t>
+          <t>3215421</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3284063</t>
+          <t>3282261</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6516621</t>
+          <t>6516450</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6597432</t>
+          <t>6600488</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15830</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35490</t>
+          <t>34962</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>46191</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277931</t>
+          <t>276783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289986</t>
+          <t>289915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253213</t>
+          <t>253741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272145</t>
+          <t>272656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>536202</t>
+          <t>536273</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559805</t>
+          <t>559149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23325</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46554</t>
+          <t>46347</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29589</t>
+          <t>29217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56444</t>
+          <t>55952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487757</t>
+          <t>487923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499417</t>
+          <t>499381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476530</t>
+          <t>476737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499759</t>
+          <t>500402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>969215</t>
+          <t>969707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>996070</t>
+          <t>996442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24191</t>
+          <t>23190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26145</t>
+          <t>26661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311690</t>
+          <t>310057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312118</t>
+          <t>313119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328429</t>
+          <t>328365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628729</t>
+          <t>628213</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645260</t>
+          <t>645474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24124</t>
+          <t>24836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47714</t>
+          <t>47289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356300</t>
+          <t>356389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367070</t>
+          <t>367042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347777</t>
+          <t>348473</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368979</t>
+          <t>369435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709533</t>
+          <t>709958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>733123</t>
+          <t>732411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19207</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12714</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30130</t>
+          <t>29609</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>22332</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42530</t>
+          <t>42826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192014</t>
+          <t>191927</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205206</t>
+          <t>204702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188457</t>
+          <t>188978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205873</t>
+          <t>206128</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387278</t>
+          <t>386982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407785</t>
+          <t>407476</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34623</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37722</t>
+          <t>38314</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255020</t>
+          <t>255512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262329</t>
+          <t>262326</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238492</t>
+          <t>238559</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258143</t>
+          <t>257312</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>498516</t>
+          <t>497924</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>518680</t>
+          <t>519239</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>26996</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50371</t>
+          <t>53757</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32744</t>
+          <t>32820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>63046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637650</t>
+          <t>638000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652239</t>
+          <t>652368</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>640923</t>
+          <t>637537</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>666438</t>
+          <t>664298</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1286426</t>
+          <t>1284806</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1315108</t>
+          <t>1315032</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>16866</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>37932</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,82 +9795,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>72088</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>55842</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>90263</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>97520</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>78593</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>121342</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>4,9%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>72088</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>55782</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>89837</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>97520</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>78821</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>117912</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>740448</t>
+          <t>740651</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761214</t>
+          <t>761717</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,82 +9908,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>754079</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>735904</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>770325</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>93,24%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1507230</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1483408</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1526157</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>92,44%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>95,1%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>754079</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>736330</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>770385</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>89,13%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>93,25%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1419</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1507230</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1486838</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1525929</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57849</t>
+          <t>58629</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>91412</t>
+          <t>92928</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>223043</t>
+          <t>220920</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>283410</t>
+          <t>288598</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>290464</t>
+          <t>294186</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>362774</t>
+          <t>365908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3302938</t>
+          <t>3301422</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3336501</t>
+          <t>3335721</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3261132</t>
+          <t>3255944</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3321499</t>
+          <t>3323622</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6576118</t>
+          <t>6572984</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6648428</t>
+          <t>6644706</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>12681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25711</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>300729</t>
+          <t>301572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309773</t>
+          <t>309772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270726</t>
+          <t>270439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280678</t>
+          <t>280572</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575366</t>
+          <t>575842</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588637</t>
+          <t>588396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11385</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31687</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>40757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62174</t>
+          <t>64745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56718</t>
+          <t>57036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85567</t>
+          <t>85595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485706</t>
+          <t>485933</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>506008</t>
+          <t>506284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451551</t>
+          <t>448980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>474559</t>
+          <t>472968</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945551</t>
+          <t>945523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974400</t>
+          <t>974082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25796</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25309</t>
+          <t>25752</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43013</t>
+          <t>43430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62189</t>
+          <t>63786</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289764</t>
+          <t>290252</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306115</t>
+          <t>305698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323819</t>
+          <t>323376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602499</t>
+          <t>600902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624602</t>
+          <t>623852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26519</t>
+          <t>25528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30722</t>
+          <t>29601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23413</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49507</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>286038</t>
+          <t>287029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>304808</t>
+          <t>304233</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444665</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>463904</t>
+          <t>463497</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>738437</t>
+          <t>737757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764274</t>
+          <t>764531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172975</t>
+          <t>173349</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178067</t>
+          <t>178196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193053</t>
+          <t>193345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201075</t>
+          <t>201261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369420</t>
+          <t>369176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378495</t>
+          <t>378308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38448</t>
+          <t>39257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248935</t>
+          <t>248677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261385</t>
+          <t>261520</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234987</t>
+          <t>234504</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245700</t>
+          <t>245586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488244</t>
+          <t>487435</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>505037</t>
+          <t>504382</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18689</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39209</t>
+          <t>38531</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30955</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>86392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55893</t>
+          <t>56610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110825</t>
+          <t>112016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585070</t>
+          <t>585748</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605590</t>
+          <t>605264</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>763982</t>
+          <t>762873</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>818310</t>
+          <t>820527</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1362719</t>
+          <t>1361528</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1417651</t>
+          <t>1416934</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20756</t>
+          <t>23092</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45893</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68664</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43069</t>
+          <t>41163</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88311</t>
+          <t>86952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>907964</t>
+          <t>905628</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>924413</t>
+          <t>923459</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>646187</t>
+          <t>645851</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>668958</t>
+          <t>669016</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1555261</t>
+          <t>1556620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1600503</t>
+          <t>1602409</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>84745</t>
+          <t>85505</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>135474</t>
+          <t>134337</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>210501</t>
+          <t>214142</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>291456</t>
+          <t>293572</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>322144</t>
+          <t>323773</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>414280</t>
+          <t>413007</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3322856</t>
+          <t>3323993</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3373585</t>
+          <t>3372825</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3366246</t>
+          <t>3364130</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3447201</t>
+          <t>3443560</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6701752</t>
+          <t>6703025</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6793888</t>
+          <t>6792259</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A07-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32392</t>
+          <t>30909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>19103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39962</t>
+          <t>40753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259879</t>
+          <t>260559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270248</t>
+          <t>270163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228446</t>
+          <t>229929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247524</t>
+          <t>247571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>493886</t>
+          <t>493095</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>515196</t>
+          <t>514745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19732</t>
+          <t>20485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41042</t>
+          <t>40954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23017</t>
+          <t>24202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>46616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484186</t>
+          <t>482946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492092</t>
+          <t>492010</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462907</t>
+          <t>462995</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484217</t>
+          <t>483464</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951469</t>
+          <t>950408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974007</t>
+          <t>972822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23799</t>
+          <t>24046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29266</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306520</t>
+          <t>308007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317822</t>
+          <t>317820</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311613</t>
+          <t>311366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326575</t>
+          <t>326486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624992</t>
+          <t>625219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643062</t>
+          <t>642763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>24937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29254</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>350190</t>
+          <t>350973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357815</t>
+          <t>357819</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345325</t>
+          <t>346519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361178</t>
+          <t>361426</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700873</t>
+          <t>700702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717614</t>
+          <t>718135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35517</t>
+          <t>34929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23008</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44330</t>
+          <t>44925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>188296</t>
+          <t>187509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198876</t>
+          <t>198754</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172151</t>
+          <t>172739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192146</t>
+          <t>191490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366646</t>
+          <t>366051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>387968</t>
+          <t>388239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263627</t>
+          <t>263616</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261705</t>
+          <t>261114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273343</t>
+          <t>273944</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529184</t>
+          <t>530857</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542963</t>
+          <t>543035</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>34622</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61675</t>
+          <t>62072</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46409</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75460</t>
+          <t>76462</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>595530</t>
+          <t>595618</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>608790</t>
+          <t>608435</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>576544</t>
+          <t>576147</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>602128</t>
+          <t>603597</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1177786</t>
+          <t>1176784</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1206837</t>
+          <t>1206832</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19612</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41821</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42147</t>
+          <t>41917</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71657</t>
+          <t>72665</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66197</t>
+          <t>67626</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105297</t>
+          <t>105411</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>700956</t>
+          <t>700335</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>723165</t>
+          <t>722351</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>711854</t>
+          <t>710846</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>741364</t>
+          <t>741594</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1420991</t>
+          <t>1420877</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1460091</t>
+          <t>1458662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>55132</t>
+          <t>54910</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>88484</t>
+          <t>87621</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190996</t>
+          <t>190667</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>247695</t>
+          <t>247809</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>259067</t>
+          <t>256746</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>319516</t>
+          <t>323336</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3187041</t>
+          <t>3187904</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3220393</t>
+          <t>3220615</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3131502</t>
+          <t>3131388</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3188201</t>
+          <t>3188530</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6335206</t>
+          <t>6331386</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6395655</t>
+          <t>6397976</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31557</t>
+          <t>31169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44136</t>
+          <t>44716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>270694</t>
+          <t>270918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284303</t>
+          <t>284323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250508</t>
+          <t>250896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268290</t>
+          <t>268956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>528133</t>
+          <t>527553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>550290</t>
+          <t>550357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24630</t>
+          <t>23370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31313</t>
+          <t>31467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56830</t>
+          <t>58118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42145</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73071</t>
+          <t>73845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479856</t>
+          <t>481116</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499087</t>
+          <t>499361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465901</t>
+          <t>464613</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491418</t>
+          <t>491264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>954146</t>
+          <t>953372</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>985072</t>
+          <t>985516</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22902</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>20473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42193</t>
+          <t>43594</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31901</t>
+          <t>29757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57701</t>
+          <t>56939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300214</t>
+          <t>299862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316112</t>
+          <t>316018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>298827</t>
+          <t>297426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320981</t>
+          <t>320547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>606435</t>
+          <t>607197</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632235</t>
+          <t>634379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>28517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52799</t>
+          <t>51815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33220</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59979</t>
+          <t>57946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363135</t>
+          <t>362450</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371940</t>
+          <t>371977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>335175</t>
+          <t>336159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358626</t>
+          <t>359457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>701977</t>
+          <t>704010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728736</t>
+          <t>729796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24385</t>
+          <t>23698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45613</t>
+          <t>45133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>28770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54145</t>
+          <t>52463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198702</t>
+          <t>200089</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210439</t>
+          <t>209938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173978</t>
+          <t>174458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195206</t>
+          <t>195893</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378064</t>
+          <t>379746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>404179</t>
+          <t>403439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17760</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35327</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25334</t>
+          <t>24723</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48230</t>
+          <t>47750</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256221</t>
+          <t>255537</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268963</t>
+          <t>268860</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243813</t>
+          <t>244637</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>262794</t>
+          <t>263031</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>504891</t>
+          <t>505371</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>527787</t>
+          <t>528398</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>18461</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42083</t>
+          <t>40934</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37476</t>
+          <t>37999</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>66696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63140</t>
+          <t>61576</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100962</t>
+          <t>101005</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>620705</t>
+          <t>621854</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>643991</t>
+          <t>644327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>627195</t>
+          <t>626077</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>655297</t>
+          <t>654774</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1254599</t>
+          <t>1254556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1292421</t>
+          <t>1293985</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>32720</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41003</t>
+          <t>41409</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72133</t>
+          <t>68990</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57341</t>
+          <t>57937</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92989</t>
+          <t>94537</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>743792</t>
+          <t>744252</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>765281</t>
+          <t>764250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>749387</t>
+          <t>752530</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>780517</t>
+          <t>780111</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1505503</t>
+          <t>1503955</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1541151</t>
+          <t>1540555</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>86537</t>
+          <t>86262</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132995</t>
+          <t>133819</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>264554</t>
+          <t>262954</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>331394</t>
+          <t>334706</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>364473</t>
+          <t>362663</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>448511</t>
+          <t>444459</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3285152</t>
+          <t>3284328</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3331610</t>
+          <t>3331885</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3215421</t>
+          <t>3212109</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3282261</t>
+          <t>3283861</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6516450</t>
+          <t>6520502</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6600488</t>
+          <t>6602298</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34962</t>
+          <t>35398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23315</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>46465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276783</t>
+          <t>277935</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289915</t>
+          <t>289778</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253741</t>
+          <t>253305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272656</t>
+          <t>272205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>536273</t>
+          <t>535999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559149</t>
+          <t>559083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>13927</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22682</t>
+          <t>23614</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46347</t>
+          <t>47474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>29360</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55952</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487923</t>
+          <t>488648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>499381</t>
+          <t>499369</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476737</t>
+          <t>475610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500402</t>
+          <t>499470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>969707</t>
+          <t>969005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>996442</t>
+          <t>996299</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23190</t>
+          <t>23378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26661</t>
+          <t>26228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310057</t>
+          <t>310950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313119</t>
+          <t>312931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328365</t>
+          <t>328738</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628213</t>
+          <t>628646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645474</t>
+          <t>645523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>18398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24836</t>
+          <t>25487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47289</t>
+          <t>47200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356389</t>
+          <t>356718</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367042</t>
+          <t>367086</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348473</t>
+          <t>348379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369435</t>
+          <t>368885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709958</t>
+          <t>710047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>732411</t>
+          <t>731760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19294</t>
+          <t>19283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29609</t>
+          <t>30040</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22332</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42826</t>
+          <t>42593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191927</t>
+          <t>191938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204702</t>
+          <t>205180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188978</t>
+          <t>188547</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206128</t>
+          <t>205772</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386982</t>
+          <t>387215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407476</t>
+          <t>407948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>787</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34556</t>
+          <t>33561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>17109</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38314</t>
+          <t>36703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255512</t>
+          <t>255363</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262326</t>
+          <t>262336</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238559</t>
+          <t>239554</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257312</t>
+          <t>258445</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497924</t>
+          <t>499535</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519239</t>
+          <t>519129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26996</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53757</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32820</t>
+          <t>34627</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63046</t>
+          <t>63149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>638000</t>
+          <t>637474</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652368</t>
+          <t>652149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>637537</t>
+          <t>639107</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>664298</t>
+          <t>665296</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1284806</t>
+          <t>1284703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1315032</t>
+          <t>1313225</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16866</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37932</t>
+          <t>36237</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55842</t>
+          <t>57047</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90263</t>
+          <t>92327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78593</t>
+          <t>78933</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>121342</t>
+          <t>119325</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>740651</t>
+          <t>742346</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761717</t>
+          <t>761177</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>735904</t>
+          <t>733840</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>770325</t>
+          <t>769120</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1483408</t>
+          <t>1485425</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1526157</t>
+          <t>1525817</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58629</t>
+          <t>58476</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92928</t>
+          <t>94031</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>220920</t>
+          <t>223117</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>288598</t>
+          <t>286399</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>294186</t>
+          <t>294586</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>365908</t>
+          <t>366535</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3301422</t>
+          <t>3300319</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3335721</t>
+          <t>3335874</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3255944</t>
+          <t>3258143</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3323622</t>
+          <t>3321425</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6572984</t>
+          <t>6572357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6644706</t>
+          <t>6644306</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,22 +10767,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18035</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12681</t>
+          <t>13397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25235</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>306764</t>
+          <t>314518</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301572</t>
+          <t>309215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309772</t>
+          <t>317217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>276279</t>
+          <t>301662</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270439</t>
+          <t>295465</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280572</t>
+          <t>306342</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,27 +10880,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>583042</t>
+          <t>616180</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575842</t>
+          <t>608342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588396</t>
+          <t>621509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31460</t>
+          <t>31637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50388</t>
+          <t>51877</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40757</t>
+          <t>41702</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64745</t>
+          <t>65609</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>69658</t>
+          <t>71546</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>57405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85595</t>
+          <t>88097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>498123</t>
+          <t>509991</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>485933</t>
+          <t>498023</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>506284</t>
+          <t>517551</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>463337</t>
+          <t>493336</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448980</t>
+          <t>479604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>472968</t>
+          <t>503511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>961460</t>
+          <t>1003327</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945523</t>
+          <t>986776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974082</t>
+          <t>1017468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16769</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25308</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,27 +11418,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>34631</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25752</t>
+          <t>26721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43430</t>
+          <t>44331</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>50495</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40836</t>
+          <t>41972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63786</t>
+          <t>64363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>298791</t>
+          <t>297550</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>290252</t>
+          <t>288042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304922</t>
+          <t>303493</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,22 +11531,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>315402</t>
+          <t>321750</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305698</t>
+          <t>312050</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323376</t>
+          <t>329660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>614193</t>
+          <t>619301</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>600902</t>
+          <t>607517</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623852</t>
+          <t>629908</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>28379</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>31996</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23413</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>52657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>297905</t>
+          <t>357219</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287029</t>
+          <t>344766</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>304233</t>
+          <t>364596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>454652</t>
+          <t>398985</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>445786</t>
+          <t>389634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>463497</t>
+          <t>405257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>752557</t>
+          <t>756204</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737757</t>
+          <t>742118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764531</t>
+          <t>766958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>571</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>176490</t>
+          <t>203305</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173349</t>
+          <t>199818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178196</t>
+          <t>205094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>197834</t>
+          <t>215934</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193345</t>
+          <t>211148</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201261</t>
+          <t>219586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>374324</t>
+          <t>419238</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369176</t>
+          <t>413750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378308</t>
+          <t>423164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20959</t>
+          <t>20255</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>29596</t>
+          <t>29393</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22156</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39257</t>
+          <t>37716</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>256142</t>
+          <t>257606</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248677</t>
+          <t>250452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261520</t>
+          <t>262579</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>240955</t>
+          <t>247458</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234504</t>
+          <t>241352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245586</t>
+          <t>252527</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>497096</t>
+          <t>505064</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>487435</t>
+          <t>496741</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504382</t>
+          <t>512301</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>32949</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>47514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>70561</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86392</t>
+          <t>87230</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>88409</t>
+          <t>103510</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56610</t>
+          <t>85183</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112016</t>
+          <t>124259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>596665</t>
+          <t>686738</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585748</t>
+          <t>672173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605264</t>
+          <t>697063</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>788470</t>
+          <t>701496</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>762873</t>
+          <t>684827</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>820527</t>
+          <t>713909</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1385135</t>
+          <t>1388234</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1361528</t>
+          <t>1367485</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1416934</t>
+          <t>1406561</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23092</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>56273</t>
+          <t>64572</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>51712</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69000</t>
+          <t>78911</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>69299</t>
+          <t>80046</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41163</t>
+          <t>66500</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86952</t>
+          <t>96773</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>915695</t>
+          <t>782598</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>905628</t>
+          <t>773373</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>923459</t>
+          <t>788513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>658578</t>
+          <t>765434</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>645851</t>
+          <t>751095</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>778294</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1574273</t>
+          <t>1548032</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1556620</t>
+          <t>1531305</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1602409</t>
+          <t>1561578</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>111757</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85505</t>
+          <t>100742</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>134337</t>
+          <t>146123</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>262196</t>
+          <t>286257</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>214142</t>
+          <t>259442</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>293572</t>
+          <t>312595</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>373953</t>
+          <t>408011</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>323773</t>
+          <t>375286</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>413007</t>
+          <t>444858</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3346573</t>
+          <t>3409526</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3323993</t>
+          <t>3385157</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3372825</t>
+          <t>3430538</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3395506</t>
+          <t>3446056</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3364130</t>
+          <t>3419718</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3443560</t>
+          <t>3472871</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6742079</t>
+          <t>6855582</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6703025</t>
+          <t>6818735</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6792259</t>
+          <t>6888307</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
